--- a/forms/dist/obs_camp_station.xlsx
+++ b/forms/dist/obs_camp_station.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O142"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -460,6 +460,8 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,6 +538,16 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>parameters</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>choice_filter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>save_to</t>
         </is>
       </c>
     </row>
@@ -563,6 +575,8 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -588,6 +602,8 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -613,6 +629,8 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -638,6 +656,8 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -663,6 +683,8 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -700,6 +722,8 @@
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -733,6 +757,8 @@
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -774,6 +800,8 @@
       </c>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -815,6 +843,8 @@
       </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -840,6 +870,8 @@
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -869,6 +901,8 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -898,6 +932,8 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -935,6 +971,8 @@
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -976,6 +1014,8 @@
       </c>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1029,6 +1069,8 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1090,6 +1132,8 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1115,6 +1159,8 @@
       <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1144,6 +1190,8 @@
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1193,6 +1241,8 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1230,6 +1280,8 @@
       <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1271,6 +1323,8 @@
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1320,6 +1374,8 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1369,6 +1425,8 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1418,6 +1476,8 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1467,6 +1527,8 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1492,6 +1554,8 @@
       <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1521,6 +1585,8 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1550,6 +1616,8 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1587,6 +1655,8 @@
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1628,6 +1698,8 @@
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1677,6 +1749,8 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1722,6 +1796,8 @@
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1747,6 +1823,8 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1784,6 +1862,8 @@
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1833,6 +1913,8 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1882,6 +1964,8 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1907,6 +1991,8 @@
       <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1936,6 +2022,8 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1973,6 +2061,8 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2014,6 +2104,8 @@
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2055,6 +2147,8 @@
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2100,6 +2194,8 @@
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2145,6 +2241,8 @@
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2186,6 +2284,8 @@
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2227,6 +2327,8 @@
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2268,6 +2370,8 @@
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2325,6 +2429,8 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2350,6 +2456,8 @@
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2391,6 +2499,8 @@
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2436,6 +2546,8 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2481,6 +2593,8 @@
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2506,6 +2620,8 @@
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2551,6 +2667,8 @@
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2576,6 +2694,8 @@
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2613,6 +2733,8 @@
       <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2650,6 +2772,8 @@
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2691,6 +2815,8 @@
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2732,6 +2858,8 @@
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2773,6 +2901,8 @@
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2810,6 +2940,8 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2851,6 +2983,8 @@
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2896,6 +3030,8 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2945,6 +3081,8 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2986,6 +3124,8 @@
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3023,6 +3163,8 @@
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3048,6 +3190,8 @@
       <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr"/>
+      <c r="Q67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3085,6 +3229,8 @@
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr"/>
+      <c r="Q68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3122,6 +3268,8 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3159,6 +3307,8 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3200,6 +3350,8 @@
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3241,6 +3393,8 @@
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3282,6 +3436,8 @@
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3319,6 +3475,8 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3344,6 +3502,8 @@
       <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr"/>
+      <c r="Q75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3373,6 +3533,8 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3414,6 +3576,8 @@
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3447,6 +3611,8 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3488,6 +3654,8 @@
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3533,6 +3701,8 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3570,6 +3740,8 @@
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3607,6 +3779,8 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3648,6 +3822,8 @@
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3673,6 +3849,8 @@
       <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="3" t="inlineStr"/>
       <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr"/>
+      <c r="Q84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3722,6 +3900,8 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3771,6 +3951,8 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3808,6 +3990,8 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -3833,6 +4017,8 @@
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="inlineStr"/>
       <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr"/>
+      <c r="Q88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3870,6 +4056,8 @@
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="inlineStr"/>
       <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -3907,6 +4095,8 @@
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3956,6 +4146,8 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3997,6 +4189,8 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4034,6 +4228,8 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4075,6 +4271,8 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -4100,6 +4298,8 @@
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="inlineStr"/>
       <c r="O95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr"/>
+      <c r="Q95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -4137,6 +4337,8 @@
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr"/>
+      <c r="P96" s="3" t="inlineStr"/>
+      <c r="Q96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4186,6 +4388,8 @@
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4231,6 +4435,8 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4268,6 +4474,8 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4305,6 +4513,8 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4346,6 +4556,8 @@
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4383,6 +4595,8 @@
       <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4420,6 +4634,8 @@
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -4445,6 +4661,8 @@
       <c r="M104" s="3" t="inlineStr"/>
       <c r="N104" s="3" t="inlineStr"/>
       <c r="O104" s="3" t="inlineStr"/>
+      <c r="P104" s="3" t="inlineStr"/>
+      <c r="Q104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -4470,6 +4688,8 @@
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="inlineStr"/>
       <c r="O105" s="3" t="inlineStr"/>
+      <c r="P105" s="3" t="inlineStr"/>
+      <c r="Q105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4507,6 +4727,8 @@
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -4544,6 +4766,8 @@
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="inlineStr"/>
       <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="3" t="inlineStr"/>
+      <c r="Q107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -4581,6 +4805,8 @@
         </is>
       </c>
       <c r="O108" s="3" t="inlineStr"/>
+      <c r="P108" s="3" t="inlineStr"/>
+      <c r="Q108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4622,6 +4848,8 @@
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4663,6 +4891,8 @@
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4704,6 +4934,8 @@
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4745,6 +4977,8 @@
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4794,6 +5028,8 @@
       <c r="M113" s="2" t="inlineStr"/>
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -4819,6 +5055,8 @@
       <c r="M114" s="3" t="inlineStr"/>
       <c r="N114" s="3" t="inlineStr"/>
       <c r="O114" s="3" t="inlineStr"/>
+      <c r="P114" s="3" t="inlineStr"/>
+      <c r="Q114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4856,6 +5094,8 @@
       <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -4893,6 +5133,8 @@
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr"/>
+      <c r="P116" s="3" t="inlineStr"/>
+      <c r="Q116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4926,6 +5168,8 @@
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4967,6 +5211,8 @@
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5008,6 +5254,8 @@
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -5033,6 +5281,8 @@
       <c r="M120" s="3" t="inlineStr"/>
       <c r="N120" s="3" t="inlineStr"/>
       <c r="O120" s="3" t="inlineStr"/>
+      <c r="P120" s="3" t="inlineStr"/>
+      <c r="Q120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5062,6 +5312,8 @@
       <c r="M121" s="2" t="inlineStr"/>
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -5099,6 +5351,8 @@
         </is>
       </c>
       <c r="O122" s="3" t="inlineStr"/>
+      <c r="P122" s="3" t="inlineStr"/>
+      <c r="Q122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5140,6 +5394,8 @@
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5181,6 +5437,8 @@
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -5206,6 +5464,8 @@
       <c r="M125" s="3" t="inlineStr"/>
       <c r="N125" s="3" t="inlineStr"/>
       <c r="O125" s="3" t="inlineStr"/>
+      <c r="P125" s="3" t="inlineStr"/>
+      <c r="Q125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -5243,6 +5503,8 @@
         </is>
       </c>
       <c r="O126" s="3" t="inlineStr"/>
+      <c r="P126" s="3" t="inlineStr"/>
+      <c r="Q126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5280,6 +5542,8 @@
       <c r="M127" s="2" t="inlineStr"/>
       <c r="N127" s="2" t="inlineStr"/>
       <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5317,6 +5581,8 @@
       <c r="M128" s="2" t="inlineStr"/>
       <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -5342,6 +5608,8 @@
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="inlineStr"/>
       <c r="O129" s="3" t="inlineStr"/>
+      <c r="P129" s="3" t="inlineStr"/>
+      <c r="Q129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5371,6 +5639,8 @@
       <c r="M130" s="2" t="inlineStr"/>
       <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5416,6 +5686,8 @@
       <c r="M131" s="2" t="inlineStr"/>
       <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5453,6 +5725,8 @@
       <c r="M132" s="2" t="inlineStr"/>
       <c r="N132" s="2" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -5478,6 +5752,8 @@
       <c r="M133" s="3" t="inlineStr"/>
       <c r="N133" s="3" t="inlineStr"/>
       <c r="O133" s="3" t="inlineStr"/>
+      <c r="P133" s="3" t="inlineStr"/>
+      <c r="Q133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -5515,6 +5791,8 @@
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="inlineStr"/>
       <c r="O134" s="3" t="inlineStr"/>
+      <c r="P134" s="3" t="inlineStr"/>
+      <c r="Q134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5552,6 +5830,8 @@
       <c r="M135" s="2" t="inlineStr"/>
       <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr"/>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5593,6 +5873,8 @@
       <c r="M136" s="2" t="inlineStr"/>
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5638,6 +5920,8 @@
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr"/>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5675,6 +5959,8 @@
       <c r="M138" s="2" t="inlineStr"/>
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5716,6 +6002,8 @@
       <c r="M139" s="2" t="inlineStr"/>
       <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5757,6 +6045,8 @@
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -5782,6 +6072,8 @@
       <c r="M141" s="3" t="inlineStr"/>
       <c r="N141" s="3" t="inlineStr"/>
       <c r="O141" s="3" t="inlineStr"/>
+      <c r="P141" s="3" t="inlineStr"/>
+      <c r="Q141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5815,6 +6107,8 @@
       <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr"/>
       <c r="O142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
